--- a/Backend/report.xlsx
+++ b/Backend/report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,24 +424,64 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>new</v>
+        <v>New</v>
       </c>
       <c r="C2" t="str">
         <v>Material</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F2">
-        <v>6000</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Helper</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Labour</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>400</v>
+      </c>
+      <c r="F3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Cement</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Material</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>400</v>
+      </c>
+      <c r="F4">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>